--- a/Airlines-Services/airlines/management/commands/AirlineRoutes/AirlineRoutesAirportsDepartureArrival.xlsx
+++ b/Airlines-Services/airlines/management/commands/AirlineRoutes/AirlineRoutesAirportsDepartureArrival.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\git\flight-profile\airline\management\commands\AirlineRoutes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\git\Airlines-Services\Airlines-Services\airlines\management\commands\AirlineRoutes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6268EB03-FF52-4376-A9AA-1880EBEF47F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81415240-4DAD-4B18-9F6E-31DB6F8011E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="67">
   <si>
     <t>Departure Airport</t>
   </si>
@@ -222,6 +222,18 @@
   </si>
   <si>
     <t>LPFR</t>
+  </si>
+  <si>
+    <t>Bari-Puglia</t>
+  </si>
+  <si>
+    <t>Paris Orly</t>
+  </si>
+  <si>
+    <t>LIBD</t>
+  </si>
+  <si>
+    <t>LFPO</t>
   </si>
 </sst>
 </file>
@@ -576,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.81640625" customWidth="1"/>
@@ -1011,6 +1023,23 @@
         <v>52</v>
       </c>
     </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
